--- a/data/trans_orig/IP16B06-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP16B06-Clase-trans_orig.xlsx
@@ -5425,7 +5425,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>634</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -5440,7 +5440,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>21,5%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -5495,7 +5495,7 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2508</t>
+          <t>2570</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
@@ -5510,7 +5510,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>44,67%</t>
+          <t>45,78%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -5543,7 +5543,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2947</t>
+          <t>2313</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5558,7 +5558,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>78,5%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5613,7 +5613,7 @@
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>3106</t>
+          <t>3044</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5628,7 +5628,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>55,33%</t>
+          <t>54,22%</t>
         </is>
       </c>
     </row>
